--- a/UPB Lista 2026.xlsx
+++ b/UPB Lista 2026.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1779109555" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1779109555" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="selection"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1779109555" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1779109555"/>
+      <pm:revision xmlns:pm="smNativeData" day="1779278746" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1779278746" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="selection"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1779278746" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1779278746"/>
       <pm:pdfExportOpt xmlns:pm="smNativeData" pagesRangeIndex="1" pagesSelectionIndex="0" qualityIndex="2" embedFonts="2" useJpegs="0" useSubsetFonts="1" useAlpha="1" relativeLinks="0" taggedPdf="1" pane="0" zoom="0" zoomScale="100" layout="0" includeDoc="0" viewFlags="0" openViewer="1" jpegQuality="90" flags="252" exportWsNames="1" dpi="2" resample="1" name="C:\Users\luigi\OneDrive\Escritorio\UPB\2026\UPB Lista 2026.pdf" map="1"/>
     </ext>
   </extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="111">
   <si>
     <t>Miércoles</t>
   </si>
@@ -42,6 +42,12 @@
   </si>
   <si>
     <t>Lunes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jueves </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viernes </t>
   </si>
   <si>
     <t>Totales</t>
@@ -389,7 +395,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1779109555" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1779278746" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -404,7 +410,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1779109555" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1779278746" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="240" lang="default"/>
             <pm:ea face="SimSun" sz="240" lang="default"/>
@@ -419,7 +425,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1779109555" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1779278746" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -435,7 +441,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1779109555" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1779278746" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="160" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -450,7 +456,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1779109555" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1779278746" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="160" lang="default"/>
             <pm:ea face="SimSun" sz="160" lang="default"/>
@@ -466,7 +472,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1779109555" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1779278746" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" weight="bold"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -481,7 +487,7 @@
       <sz val="8"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1779109555" fgClr="B3B3B3" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1779278746" fgClr="B3B3B3" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="160" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -490,7 +496,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,7 +509,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -514,7 +520,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -528,18 +534,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="0000FF00" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="100" fgClr="0000FF00" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -550,7 +545,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -561,7 +556,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="82" fgClr="0000FF00" bgLvl="18" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="82" fgClr="0000FF00" bgLvl="18" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -572,7 +567,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="38" fgClr="0000FFFF" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="38" fgClr="0000FFFF" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -583,7 +578,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="38" fgClr="000000FF" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="38" fgClr="000000FF" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -594,7 +589,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -605,7 +600,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="38" fgClr="00FF00FF" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="38" fgClr="00FF00FF" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -619,7 +614,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="76" fgClr="0000FF00" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="76" fgClr="0000FF00" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -630,7 +625,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -641,7 +636,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -652,7 +647,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -666,7 +661,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -677,7 +672,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -688,7 +683,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="76" fgClr="0000FFFF" bgLvl="24" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -699,7 +694,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="71" fgClr="00FFFFFF" bgLvl="29" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="71" fgClr="00FFFFFF" bgLvl="29" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -710,7 +705,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="71" fgClr="00FFFFFF" bgLvl="29" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="71" fgClr="00FFFFFF" bgLvl="29" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -721,29 +716,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="71" fgClr="00FFFFFF" bgLvl="29" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="100" fgClr="00FFFF00" bgLvl="0" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="71" fgClr="00FFFFFF" bgLvl="29" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -754,7 +727,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="38" fgClr="00FF00FF" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="38" fgClr="00FF00FF" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -765,7 +738,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1779109555" type="1" fgLvl="38" fgClr="00FF00FF" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="38" fgClr="00FF00FF" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -773,8 +746,19 @@
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1779278746" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="27">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -790,7 +774,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -809,7 +793,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -833,7 +817,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -856,7 +840,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -879,7 +863,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -898,7 +882,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -917,7 +901,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -936,7 +920,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -955,7 +939,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -974,7 +958,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -993,26 +977,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -1031,7 +996,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1055,7 +1020,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -1074,7 +1039,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1098,7 +1063,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1121,7 +1086,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1145,7 +1110,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1168,7 +1133,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1191,7 +1156,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1214,7 +1179,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -1233,7 +1198,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -1252,7 +1217,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1276,7 +1241,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1299,7 +1264,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1323,7 +1288,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1338,7 +1303,7 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="none">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
@@ -1346,8 +1311,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          <pm:border xmlns:pm="smNativeData" id="1779278746">
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
             <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
@@ -1356,48 +1320,21 @@
       </extLst>
     </border>
     <border>
-      <left style="thin">
+      <left style="none">
         <color rgb="FF000000"/>
       </left>
       <right style="none">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top style="none">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
+      <bottom style="none">
         <color rgb="FF000000"/>
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1779109555">
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
+          <pm:border xmlns:pm="smNativeData" id="1779278746"/>
         </ext>
       </extLst>
     </border>
@@ -1405,7 +1342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1418,59 +1355,61 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="19" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="20" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="21" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="27" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="28" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="24" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -1478,10 +1417,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1779109555" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1779278746" count="1">
         <pm:charStyle name="Normal" fontId="0"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1779109555" count="10">
+      <pm:colors xmlns:pm="smNativeData" id="1779278746" count="10">
         <pm:color name="Color 24" rgb="FFFF9E"/>
         <pm:color name="Color 25" rgb="9EFF9E"/>
         <pm:color name="Color 26" rgb="A3A300"/>
@@ -1754,14 +1693,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:AE48"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="13.45"/>
   <cols>
     <col min="1" max="1" width="1.864865" customWidth="1"/>
     <col min="2" max="3" width="2.207207" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="2" max="3" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="2" max="3" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
@@ -1770,56 +1709,56 @@
     <col min="6" max="6" width="8.684685" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="6" max="6" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="6" max="6" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
     <col min="7" max="7" width="8.036036" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="7" max="7" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="7" max="7" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
     <col min="8" max="8" width="9.162162" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="8" max="8" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="8" max="8" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
     <col min="9" max="9" width="9.252252" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="9" max="9" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="9" max="9" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
     <col min="10" max="10" width="8.036036" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="10" max="10" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="10" max="10" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
     <col min="11" max="11" width="24.900901" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="11" max="11" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="11" max="11" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
     <col min="12" max="12" width="23.171171" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="12" max="12" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="12" max="12" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
     <col min="13" max="13" width="13.504505" hidden="1" customWidth="1">
       <extLst>
         <ext uri="smNativeData">
-          <pm:columnDef xmlns:pm="smNativeData" id="1779109555" min="13" max="13" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:columnDef xmlns:pm="smNativeData" id="1779278746" min="13" max="13" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </col>
@@ -1828,11 +1767,11 @@
     <col min="24" max="24" width="6.306306" customWidth="1"/>
     <col min="25" max="25" width="6.414414" customWidth="1"/>
     <col min="26" max="26" width="6.981982" customWidth="1"/>
-    <col min="27" max="30" width="6.414414" customWidth="1"/>
-    <col min="31" max="31" width="6.981982" customWidth="1"/>
+    <col min="27" max="35" width="6.414414" customWidth="1"/>
+    <col min="36" max="36" width="6.981982" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:31">
+    <row r="1" spans="6:36">
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -1891,33 +1830,48 @@
       <c r="AD1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="AE1" s="37" t="s">
+      <c r="AE1" s="24" t="s">
         <v>6</v>
       </c>
+      <c r="AF1" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ1" s="37" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:36">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
       <c r="K2" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="21"/>
@@ -1972,9 +1926,24 @@
       <c r="AD2" s="25" t="n">
         <v>46144</v>
       </c>
-      <c r="AE2" s="37"/>
+      <c r="AE2" s="25" t="n">
+        <v>46149</v>
+      </c>
+      <c r="AF2" s="23" t="n">
+        <v>46150</v>
+      </c>
+      <c r="AG2" s="23" t="n">
+        <v>46154</v>
+      </c>
+      <c r="AH2" s="25" t="n">
+        <v>46158</v>
+      </c>
+      <c r="AI2" s="25" t="n">
+        <v>46161</v>
+      </c>
+      <c r="AJ2" s="37"/>
     </row>
-    <row r="3" spans="1:31" s="0" customFormat="1">
+    <row r="3" spans="1:36" s="0" customFormat="1">
       <c r="A3" s="6"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1982,20 +1951,20 @@
         <v>1</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="38"/>
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
       <c r="J3" s="38"/>
       <c r="K3" s="12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M3" s="16"/>
       <c r="N3" s="39"/>
@@ -2021,12 +1990,17 @@
       <c r="AD3" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE3" s="16">
-        <f>SUM(O3:AD3)</f>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
+      <c r="AJ3" s="16">
+        <f>SUM(O3:AI3)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:36">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="26"/>
@@ -2034,20 +2008,20 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M4" s="16"/>
       <c r="N4" s="16"/>
@@ -2079,12 +2053,21 @@
       <c r="AB4" s="12"/>
       <c r="AC4" s="16"/>
       <c r="AD4" s="24"/>
-      <c r="AE4" s="16">
-        <f>SUM(O4:AD4)</f>
-        <v>6</v>
+      <c r="AE4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="16">
+        <f>SUM(O4:AI4)</f>
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:36">
       <c r="A5" s="6"/>
       <c r="B5" s="5"/>
       <c r="C5" s="26"/>
@@ -2092,24 +2075,24 @@
         <v>3</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
@@ -2145,12 +2128,19 @@
       <c r="AD5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" s="16">
-        <f>SUM(O5:AD5)</f>
-        <v>8</v>
+      <c r="AE5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
+      <c r="AJ5" s="16">
+        <f>SUM(O5:AI5)</f>
+        <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:36">
       <c r="A6" s="6"/>
       <c r="B6" s="5"/>
       <c r="C6" s="26"/>
@@ -2158,7 +2148,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -2182,17 +2172,24 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
-      <c r="AB6" s="12" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB6" s="12"/>
       <c r="AC6" s="16"/>
       <c r="AD6" s="24"/>
-      <c r="AE6" s="16">
-        <f>SUM(O6:AD6)</f>
-        <v>1</v>
+      <c r="AE6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="16">
+        <f>SUM(O6:AI6)</f>
+        <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:36">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="26"/>
@@ -2200,22 +2197,22 @@
         <v>5</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
@@ -2243,12 +2240,21 @@
       <c r="AB7" s="12"/>
       <c r="AC7" s="16"/>
       <c r="AD7" s="24"/>
-      <c r="AE7" s="16">
-        <f>SUM(O7:AD7)</f>
-        <v>4</v>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" s="24"/>
+      <c r="AJ7" s="16">
+        <f>SUM(O7:AI7)</f>
+        <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="8" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A8" s="6"/>
       <c r="B8" s="27"/>
       <c r="C8" s="27"/>
@@ -2256,17 +2262,17 @@
         <v>6</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G8" s="28"/>
       <c r="H8" s="28"/>
       <c r="I8" s="28"/>
       <c r="J8" s="28"/>
       <c r="K8" s="29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L8" s="29"/>
       <c r="M8" s="30"/>
@@ -2293,17 +2299,22 @@
       <c r="AB8" s="29"/>
       <c r="AC8" s="30"/>
       <c r="AD8" s="31"/>
-      <c r="AE8" s="30">
-        <f>SUM(O8:AD8)</f>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="16">
+        <f>SUM(O8:AI8)</f>
         <v>3</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="8" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="8" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:36">
       <c r="A9" s="6"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2311,25 +2322,25 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="16"/>
@@ -2360,87 +2371,97 @@
       <c r="AB9" s="12"/>
       <c r="AC9" s="16"/>
       <c r="AD9" s="24"/>
-      <c r="AE9" s="16">
-        <f>SUM(O9:AD9)</f>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="16">
+        <f>SUM(O9:AI9)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="32" customFormat="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+    <row r="10" spans="1:36" s="41" customFormat="1">
+      <c r="A10" s="42"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
       <c r="D10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="29"/>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="29"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="30">
-        <f>SUM(O10:AD10)</f>
+      <c r="E10" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" s="44"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="45"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+      <c r="R10" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="44"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="45"/>
+      <c r="V10" s="44"/>
+      <c r="W10" s="44"/>
+      <c r="X10" s="44"/>
+      <c r="Y10" s="44"/>
+      <c r="Z10" s="44"/>
+      <c r="AA10" s="44"/>
+      <c r="AB10" s="44"/>
+      <c r="AC10" s="45"/>
+      <c r="AD10" s="46"/>
+      <c r="AE10" s="46"/>
+      <c r="AF10" s="46"/>
+      <c r="AG10" s="46"/>
+      <c r="AH10" s="46"/>
+      <c r="AI10" s="46"/>
+      <c r="AJ10" s="16">
+        <f>SUM(O10:AI10)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
-      <c r="A11" s="44"/>
+    <row r="11" spans="1:36">
+      <c r="A11" s="40"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
@@ -2470,12 +2491,17 @@
       <c r="AB11" s="12"/>
       <c r="AC11" s="16"/>
       <c r="AD11" s="24"/>
-      <c r="AE11" s="16">
-        <f>SUM(O11:AD11)</f>
+      <c r="AE11" s="24"/>
+      <c r="AF11" s="24"/>
+      <c r="AG11" s="24"/>
+      <c r="AH11" s="24"/>
+      <c r="AI11" s="24"/>
+      <c r="AJ11" s="16">
+        <f>SUM(O11:AI11)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:36">
       <c r="A12" s="8"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2483,20 +2509,20 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M12" s="16"/>
       <c r="N12" s="16"/>
@@ -2526,12 +2552,17 @@
       <c r="AB12" s="12"/>
       <c r="AC12" s="16"/>
       <c r="AD12" s="24"/>
-      <c r="AE12" s="16">
-        <f>SUM(O12:AD12)</f>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
+      <c r="AH12" s="24"/>
+      <c r="AI12" s="24"/>
+      <c r="AJ12" s="16">
+        <f>SUM(O12:AI12)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="0" customFormat="1">
+    <row r="13" spans="1:36" s="0" customFormat="1">
       <c r="A13" s="8"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2539,17 +2570,17 @@
         <v>11</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G13" s="38"/>
       <c r="H13" s="38"/>
       <c r="I13" s="38"/>
       <c r="J13" s="38"/>
       <c r="K13" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="16"/>
@@ -2574,65 +2605,74 @@
       <c r="AD13" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE13" s="16">
-        <f>SUM(O13:AD13)</f>
-        <v>2</v>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="24"/>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="24"/>
+      <c r="AJ13" s="16">
+        <f>SUM(O13:AI13)</f>
+        <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="32" customFormat="1" hidden="1">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
+    <row r="14" spans="1:36" s="41" customFormat="1">
+      <c r="A14" s="42"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
       <c r="D14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E14" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" s="30"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29"/>
-      <c r="AA14" s="29"/>
-      <c r="AB14" s="29"/>
-      <c r="AC14" s="30"/>
-      <c r="AD14" s="31"/>
-      <c r="AE14" s="30">
-        <f>SUM(O14:AD14)</f>
-        <v>2</v>
-      </c>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="14" hidden="1" collapsedDB="0" collapsedOL="0"/>
-        </ext>
-      </extLst>
+      <c r="E14" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="44"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="44"/>
+      <c r="T14" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="45"/>
+      <c r="V14" s="44"/>
+      <c r="W14" s="44"/>
+      <c r="X14" s="44"/>
+      <c r="Y14" s="44"/>
+      <c r="Z14" s="44"/>
+      <c r="AA14" s="44"/>
+      <c r="AB14" s="44"/>
+      <c r="AC14" s="45"/>
+      <c r="AD14" s="46"/>
+      <c r="AE14" s="46"/>
+      <c r="AF14" s="46"/>
+      <c r="AG14" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="46"/>
+      <c r="AI14" s="46"/>
+      <c r="AJ14" s="16">
+        <f>SUM(O14:AI14)</f>
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="15" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
       <c r="C15" s="27"/>
@@ -2640,7 +2680,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F15" s="28"/>
       <c r="G15" s="28"/>
@@ -2667,17 +2707,22 @@
       <c r="AB15" s="29"/>
       <c r="AC15" s="30"/>
       <c r="AD15" s="31"/>
-      <c r="AE15" s="30">
-        <f>SUM(O15:AD15)</f>
+      <c r="AE15" s="31"/>
+      <c r="AF15" s="31"/>
+      <c r="AG15" s="31"/>
+      <c r="AH15" s="31"/>
+      <c r="AI15" s="31"/>
+      <c r="AJ15" s="16">
+        <f>SUM(O15:AI15)</f>
         <v>0</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="15" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="15" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:36">
       <c r="A16" s="9"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2685,25 +2730,25 @@
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N16" s="16"/>
       <c r="O16" s="12" t="n">
@@ -2736,12 +2781,17 @@
       <c r="AD16" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE16" s="16">
-        <f>SUM(O16:AD16)</f>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
+      <c r="AH16" s="24"/>
+      <c r="AI16" s="24"/>
+      <c r="AJ16" s="16">
+        <f>SUM(O16:AI16)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" spans="1:36">
       <c r="A17" s="9"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2749,21 +2799,21 @@
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="16"/>
@@ -2802,12 +2852,23 @@
       <c r="AD17" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE17" s="16">
-        <f>SUM(O17:AD17)</f>
-        <v>9</v>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="16">
+        <f>SUM(O17:AI17)</f>
+        <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" spans="1:36">
       <c r="A18" s="9"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2815,10 +2876,10 @@
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -2850,12 +2911,19 @@
       </c>
       <c r="AC18" s="16"/>
       <c r="AD18" s="24"/>
-      <c r="AE18" s="16">
-        <f>SUM(O18:AD18)</f>
-        <v>3</v>
+      <c r="AE18" s="24"/>
+      <c r="AF18" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="24"/>
+      <c r="AH18" s="24"/>
+      <c r="AI18" s="24"/>
+      <c r="AJ18" s="16">
+        <f>SUM(O18:AI18)</f>
+        <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" spans="1:36">
       <c r="A19" s="9"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
@@ -2863,17 +2931,17 @@
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="16"/>
@@ -2916,68 +2984,92 @@
       <c r="AD19" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE19" s="16">
-        <f>SUM(O19:AD19)</f>
-        <v>11</v>
+      <c r="AE19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="24"/>
+      <c r="AJ19" s="16">
+        <f>SUM(O19:AI19)</f>
+        <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:31" s="33" customFormat="1">
+    <row r="20" spans="1:36" s="33" customFormat="1">
       <c r="A20" s="11"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E20" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="41" t="s">
+      <c r="E20" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="L20" s="41"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" s="41"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="42"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="42">
-        <f>SUM(O20:AD20)</f>
-        <v>6</v>
+      <c r="F20" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="12"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="12"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="12"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="24"/>
+      <c r="AE20" s="24"/>
+      <c r="AF20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="24"/>
+      <c r="AJ20" s="16">
+        <f>SUM(O20:AI20)</f>
+        <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" spans="1:36">
       <c r="A21" s="11"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -2985,21 +3077,21 @@
         <v>19</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="16"/>
@@ -3030,12 +3122,21 @@
       <c r="AB21" s="12"/>
       <c r="AC21" s="16"/>
       <c r="AD21" s="24"/>
-      <c r="AE21" s="16">
-        <f>SUM(O21:AD21)</f>
-        <v>5</v>
+      <c r="AE21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="24"/>
+      <c r="AG21" s="24"/>
+      <c r="AH21" s="24"/>
+      <c r="AI21" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" s="16">
+        <f>SUM(O21:AI21)</f>
+        <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="22" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A22" s="11"/>
       <c r="B22" s="27"/>
       <c r="C22" s="27"/>
@@ -3043,10 +3144,10 @@
         <v>20</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G22" s="28"/>
       <c r="H22" s="28"/>
@@ -3074,17 +3175,22 @@
       <c r="AB22" s="29"/>
       <c r="AC22" s="30"/>
       <c r="AD22" s="31"/>
-      <c r="AE22" s="30">
-        <f>SUM(O22:AD22)</f>
-        <v>1</v>
-      </c>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="22" hidden="1" collapsedDB="0" collapsedOL="0"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="31"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="16">
+        <f>SUM(O22:AI22)</f>
+        <v>1</v>
+      </c>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="22" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="23" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="23" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A23" s="11"/>
       <c r="B23" s="27"/>
       <c r="C23" s="27"/>
@@ -3092,10 +3198,10 @@
         <v>21</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G23" s="28"/>
       <c r="H23" s="28"/>
@@ -3121,17 +3227,22 @@
       <c r="AB23" s="29"/>
       <c r="AC23" s="30"/>
       <c r="AD23" s="31"/>
-      <c r="AE23" s="30">
-        <f>SUM(O23:AD23)</f>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="31"/>
+      <c r="AH23" s="31"/>
+      <c r="AI23" s="31"/>
+      <c r="AJ23" s="16">
+        <f>SUM(O23:AI23)</f>
         <v>0</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="23" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="23" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="24" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="24" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A24" s="11"/>
       <c r="B24" s="27"/>
       <c r="C24" s="27"/>
@@ -3139,10 +3250,10 @@
         <v>22</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G24" s="28"/>
       <c r="H24" s="28"/>
@@ -3172,17 +3283,22 @@
       <c r="AB24" s="29"/>
       <c r="AC24" s="30"/>
       <c r="AD24" s="31"/>
-      <c r="AE24" s="30">
-        <f>SUM(O24:AD24)</f>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
+      <c r="AH24" s="31"/>
+      <c r="AI24" s="31"/>
+      <c r="AJ24" s="16">
+        <f>SUM(O24:AI24)</f>
         <v>2</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="24" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="24" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:36">
       <c r="A25" s="11"/>
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
@@ -3190,10 +3306,10 @@
         <v>23</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -3231,12 +3347,27 @@
       <c r="AB25" s="12"/>
       <c r="AC25" s="16"/>
       <c r="AD25" s="24"/>
-      <c r="AE25" s="16">
-        <f>SUM(O25:AD25)</f>
-        <v>6</v>
+      <c r="AE25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="16">
+        <f>SUM(O25:AI25)</f>
+        <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" spans="1:36">
       <c r="A26" s="11"/>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -3244,17 +3375,17 @@
         <v>24</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="16"/>
@@ -3285,12 +3416,21 @@
       <c r="AD26" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE26" s="16">
-        <f>SUM(O26:AD26)</f>
-        <v>5</v>
+      <c r="AE26" s="24"/>
+      <c r="AF26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="24"/>
+      <c r="AH26" s="24"/>
+      <c r="AI26" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" s="16">
+        <f>SUM(O26:AI26)</f>
+        <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" spans="1:36">
       <c r="A27" s="11"/>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -3298,17 +3438,17 @@
         <v>25</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="16"/>
@@ -3349,12 +3489,21 @@
       <c r="AD27" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE27" s="16">
-        <f>SUM(O27:AD27)</f>
-        <v>10</v>
+      <c r="AE27" s="24"/>
+      <c r="AF27" s="24"/>
+      <c r="AG27" s="24"/>
+      <c r="AH27" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" s="16">
+        <f>SUM(O27:AI27)</f>
+        <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:31" s="0" customFormat="1">
+    <row r="28" spans="1:36" s="0" customFormat="1">
       <c r="A28" s="11"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -3362,17 +3511,17 @@
         <v>26</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
       <c r="I28" s="38"/>
       <c r="J28" s="38"/>
       <c r="K28" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="16"/>
@@ -3401,12 +3550,21 @@
       <c r="AB28" s="12"/>
       <c r="AC28" s="16"/>
       <c r="AD28" s="24"/>
-      <c r="AE28" s="16">
-        <f>SUM(O28:AD28)</f>
-        <v>4</v>
+      <c r="AE28" s="24"/>
+      <c r="AF28" s="24"/>
+      <c r="AG28" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" s="24"/>
+      <c r="AI28" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" s="16">
+        <f>SUM(O28:AI28)</f>
+        <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="29" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A29" s="11"/>
       <c r="B29" s="27"/>
       <c r="C29" s="27"/>
@@ -3414,10 +3572,10 @@
         <v>27</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G29" s="28"/>
       <c r="H29" s="28"/>
@@ -3443,17 +3601,22 @@
       <c r="AB29" s="29"/>
       <c r="AC29" s="30"/>
       <c r="AD29" s="31"/>
-      <c r="AE29" s="30">
-        <f>SUM(O29:AD29)</f>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="31"/>
+      <c r="AH29" s="31"/>
+      <c r="AI29" s="31"/>
+      <c r="AJ29" s="16">
+        <f>SUM(O29:AI29)</f>
         <v>0</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="29" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="29" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="30" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="30" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A30" s="11"/>
       <c r="B30" s="27"/>
       <c r="C30" s="27"/>
@@ -3461,10 +3624,10 @@
         <v>28</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G30" s="28"/>
       <c r="H30" s="28"/>
@@ -3490,17 +3653,22 @@
       <c r="AB30" s="29"/>
       <c r="AC30" s="30"/>
       <c r="AD30" s="31"/>
-      <c r="AE30" s="30">
-        <f>SUM(O30:AD30)</f>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="31"/>
+      <c r="AH30" s="31"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="16">
+        <f>SUM(O30:AI30)</f>
         <v>0</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="30" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="30" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" spans="1:36">
       <c r="A31" s="11"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -3508,20 +3676,20 @@
         <v>29</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
@@ -3563,12 +3731,25 @@
       <c r="AD31" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE31" s="16">
-        <f>SUM(O31:AD31)</f>
-        <v>11</v>
+      <c r="AE31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="24"/>
+      <c r="AH31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" s="16">
+        <f>SUM(O31:AI31)</f>
+        <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" spans="1:36">
       <c r="A32" s="11"/>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -3576,20 +3757,20 @@
         <v>30</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
@@ -3621,12 +3802,21 @@
       <c r="AB32" s="12"/>
       <c r="AC32" s="16"/>
       <c r="AD32" s="24"/>
-      <c r="AE32" s="16">
-        <f>SUM(O32:AD32)</f>
-        <v>6</v>
+      <c r="AE32" s="24"/>
+      <c r="AF32" s="24"/>
+      <c r="AG32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" s="24"/>
+      <c r="AJ32" s="16">
+        <f>SUM(O32:AI32)</f>
+        <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:31" s="0" customFormat="1">
+    <row r="33" spans="1:36" s="0" customFormat="1">
       <c r="A33" s="11"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -3634,19 +3824,19 @@
         <v>31</v>
       </c>
       <c r="E33" s="38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F33" s="38" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G33" s="38" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H33" s="38"/>
       <c r="I33" s="38"/>
       <c r="J33" s="38"/>
       <c r="K33" s="18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L33" s="18"/>
       <c r="M33" s="16"/>
@@ -3673,12 +3863,17 @@
       <c r="AB33" s="12"/>
       <c r="AC33" s="16"/>
       <c r="AD33" s="24"/>
-      <c r="AE33" s="16">
-        <f>SUM(O33:AD33)</f>
+      <c r="AE33" s="24"/>
+      <c r="AF33" s="24"/>
+      <c r="AG33" s="24"/>
+      <c r="AH33" s="24"/>
+      <c r="AI33" s="24"/>
+      <c r="AJ33" s="16">
+        <f>SUM(O33:AI33)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="34" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A34" s="11"/>
       <c r="B34" s="27"/>
       <c r="C34" s="27"/>
@@ -3686,13 +3881,13 @@
         <v>32</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H34" s="28"/>
       <c r="I34" s="28"/>
@@ -3719,17 +3914,22 @@
       <c r="AB34" s="29"/>
       <c r="AC34" s="30"/>
       <c r="AD34" s="31"/>
-      <c r="AE34" s="30">
-        <f>SUM(O34:AD34)</f>
-        <v>1</v>
-      </c>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="34" hidden="1" collapsedDB="0" collapsedOL="0"/>
+      <c r="AE34" s="31"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="31"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="16">
+        <f>SUM(O34:AI34)</f>
+        <v>1</v>
+      </c>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="34" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="35" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="35" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A35" s="11"/>
       <c r="B35" s="27"/>
       <c r="C35" s="27"/>
@@ -3737,16 +3937,16 @@
         <v>33</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H35" s="28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I35" s="28"/>
       <c r="J35" s="28"/>
@@ -3772,71 +3972,85 @@
       <c r="AB35" s="29"/>
       <c r="AC35" s="30"/>
       <c r="AD35" s="31"/>
-      <c r="AE35" s="30">
-        <f>SUM(O35:AD35)</f>
-        <v>1</v>
-      </c>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="35" hidden="1" collapsedDB="0" collapsedOL="0"/>
+      <c r="AE35" s="31"/>
+      <c r="AF35" s="31"/>
+      <c r="AG35" s="31"/>
+      <c r="AH35" s="31"/>
+      <c r="AI35" s="31"/>
+      <c r="AJ35" s="16">
+        <f>SUM(O35:AI35)</f>
+        <v>1</v>
+      </c>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="35" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="36" spans="1:31" s="33" customFormat="1">
+    <row r="36" spans="1:36" s="33" customFormat="1">
       <c r="A36" s="11"/>
       <c r="B36" s="10"/>
       <c r="C36" s="10"/>
       <c r="D36" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E36" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="F36" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="H36" s="40" t="s">
+      <c r="E36" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="I36" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="40" t="s">
+      <c r="F36" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="41"/>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" s="43"/>
-      <c r="U36" s="42"/>
-      <c r="V36" s="41"/>
-      <c r="W36" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="X36" s="41"/>
-      <c r="Y36" s="41"/>
-      <c r="Z36" s="41"/>
-      <c r="AA36" s="41"/>
-      <c r="AB36" s="41"/>
-      <c r="AC36" s="42"/>
-      <c r="AD36" s="43"/>
-      <c r="AE36" s="42">
-        <f>SUM(O36:AD36)</f>
-        <v>2</v>
+      <c r="H36" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="I36" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="12"/>
+      <c r="R36" s="12"/>
+      <c r="S36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="24"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" s="12"/>
+      <c r="Y36" s="12"/>
+      <c r="Z36" s="12"/>
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="12"/>
+      <c r="AC36" s="16"/>
+      <c r="AD36" s="24"/>
+      <c r="AE36" s="24"/>
+      <c r="AF36" s="24"/>
+      <c r="AG36" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH36" s="24"/>
+      <c r="AI36" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="16">
+        <f>SUM(O36:AI36)</f>
+        <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="37" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A37" s="11"/>
       <c r="B37" s="27"/>
       <c r="C37" s="27"/>
@@ -3844,10 +4058,10 @@
         <v>35</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G37" s="28"/>
       <c r="H37" s="28"/>
@@ -3875,17 +4089,22 @@
       <c r="AB37" s="29"/>
       <c r="AC37" s="30"/>
       <c r="AD37" s="31"/>
-      <c r="AE37" s="30">
-        <f>SUM(O37:AD37)</f>
-        <v>1</v>
-      </c>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="37" hidden="1" collapsedDB="0" collapsedOL="0"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="31"/>
+      <c r="AH37" s="31"/>
+      <c r="AI37" s="31"/>
+      <c r="AJ37" s="16">
+        <f>SUM(O37:AI37)</f>
+        <v>1</v>
+      </c>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="37" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="38" spans="1:31" s="0" customFormat="1">
+    <row r="38" spans="1:36" s="0" customFormat="1">
       <c r="A38" s="11"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -3893,19 +4112,19 @@
         <v>36</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G38" s="38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H38" s="38"/>
       <c r="I38" s="38"/>
       <c r="J38" s="38"/>
       <c r="K38" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L38" s="12"/>
       <c r="M38" s="16"/>
@@ -3932,12 +4151,17 @@
       <c r="AB38" s="12"/>
       <c r="AC38" s="16"/>
       <c r="AD38" s="24"/>
-      <c r="AE38" s="16">
-        <f>SUM(O38:AD38)</f>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="16">
+        <f>SUM(O38:AI38)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" spans="1:36">
       <c r="A39" s="11"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -3945,25 +4169,25 @@
         <v>37</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K39" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="16"/>
@@ -3998,12 +4222,21 @@
       <c r="AD39" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE39" s="16">
-        <f>SUM(O39:AD39)</f>
-        <v>7</v>
+      <c r="AE39" s="24"/>
+      <c r="AF39" s="24"/>
+      <c r="AG39" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH39" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="24"/>
+      <c r="AJ39" s="16">
+        <f>SUM(O39:AI39)</f>
+        <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:31" s="0" customFormat="1">
+    <row r="40" spans="1:36" s="0" customFormat="1">
       <c r="A40" s="11"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -4011,22 +4244,22 @@
         <v>38</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F40" s="38" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H40" s="38"/>
       <c r="I40" s="38"/>
       <c r="J40" s="38"/>
       <c r="K40" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M40" s="16"/>
       <c r="N40" s="16"/>
@@ -4048,12 +4281,21 @@
       <c r="AB40" s="12"/>
       <c r="AC40" s="16"/>
       <c r="AD40" s="24"/>
-      <c r="AE40" s="16">
-        <f>SUM(O40:AD40)</f>
-        <v>1</v>
+      <c r="AE40" s="24"/>
+      <c r="AF40" s="24"/>
+      <c r="AG40" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH40" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI40" s="24"/>
+      <c r="AJ40" s="16">
+        <f>SUM(O40:AI40)</f>
+        <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" spans="1:36">
       <c r="A41" s="11"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -4061,10 +4303,10 @@
         <v>39</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
@@ -4094,12 +4336,27 @@
       <c r="AD41" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE41" s="16">
-        <f>SUM(O41:AD41)</f>
-        <v>2</v>
+      <c r="AE41" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG41" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH41" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI41" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="16">
+        <f>SUM(O41:AI41)</f>
+        <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="42" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A42" s="27"/>
       <c r="B42" s="27"/>
       <c r="C42" s="27"/>
@@ -4107,10 +4364,10 @@
         <v>40</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G42" s="28"/>
       <c r="H42" s="28"/>
@@ -4140,17 +4397,22 @@
       <c r="AB42" s="29"/>
       <c r="AC42" s="30"/>
       <c r="AD42" s="31"/>
-      <c r="AE42" s="30">
-        <f>SUM(O42:AD42)</f>
+      <c r="AE42" s="31"/>
+      <c r="AF42" s="31"/>
+      <c r="AG42" s="31"/>
+      <c r="AH42" s="31"/>
+      <c r="AI42" s="31"/>
+      <c r="AJ42" s="16">
+        <f>SUM(O42:AI42)</f>
         <v>2</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="42" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="42" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="43" spans="1:31" s="0" customFormat="1">
+    <row r="43" spans="1:36" s="0" customFormat="1">
       <c r="A43" s="11"/>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
@@ -4158,13 +4420,13 @@
         <v>41</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -4197,12 +4459,27 @@
       <c r="AD43" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE43" s="16">
-        <f>SUM(O43:AD43)</f>
-        <v>4</v>
+      <c r="AE43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ43" s="16">
+        <f>SUM(O43:AI43)</f>
+        <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:31" s="0" customFormat="1">
+    <row r="44" spans="1:36" s="0" customFormat="1">
       <c r="A44" s="11"/>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
@@ -4210,7 +4487,7 @@
         <v>42</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -4239,18 +4516,25 @@
       <c r="AD44" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="AE44" s="16">
-        <f>SUM(O44:AD44)</f>
-        <v>1</v>
+      <c r="AE44" s="24"/>
+      <c r="AF44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="24"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="24"/>
+      <c r="AJ44" s="16">
+        <f>SUM(O44:AI44)</f>
+        <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="45" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A45" s="27"/>
       <c r="D45" s="4" t="n">
         <v>43</v>
       </c>
       <c r="E45" s="28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F45" s="30"/>
       <c r="G45" s="30"/>
@@ -4283,23 +4567,28 @@
       <c r="AB45" s="29"/>
       <c r="AC45" s="29"/>
       <c r="AD45" s="31"/>
-      <c r="AE45" s="30">
-        <f>SUM(O45:AD45)</f>
+      <c r="AE45" s="31"/>
+      <c r="AF45" s="31"/>
+      <c r="AG45" s="31"/>
+      <c r="AH45" s="31"/>
+      <c r="AI45" s="31"/>
+      <c r="AJ45" s="16">
+        <f>SUM(O45:AI45)</f>
         <v>3</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="45" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="45" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="46" spans="1:31" s="32" customFormat="1" hidden="1">
+    <row r="46" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A46" s="27"/>
       <c r="D46" s="4" t="n">
         <v>44</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F46" s="30"/>
       <c r="G46" s="30"/>
@@ -4330,23 +4619,28 @@
       <c r="AB46" s="29"/>
       <c r="AC46" s="29"/>
       <c r="AD46" s="31"/>
-      <c r="AE46" s="29">
-        <f>SUM(O46:AD46)</f>
+      <c r="AE46" s="31"/>
+      <c r="AF46" s="31"/>
+      <c r="AG46" s="31"/>
+      <c r="AH46" s="31"/>
+      <c r="AI46" s="31"/>
+      <c r="AJ46" s="16">
+        <f>SUM(O46:AI46)</f>
         <v>2</v>
       </c>
       <extLst>
         <ext uri="smNativeData">
-          <pm:rowDef xmlns:pm="smNativeData" id="1779109555" r="46" hidden="1" collapsedDB="0" collapsedOL="0"/>
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="46" hidden="1" collapsedDB="0" collapsedOL="0"/>
         </ext>
       </extLst>
     </row>
-    <row r="47" spans="1:31" s="32" customFormat="1">
+    <row r="47" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A47" s="27"/>
       <c r="D47" s="4" t="n">
         <v>45</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N47" s="30"/>
       <c r="O47" s="30"/>
@@ -4367,18 +4661,28 @@
       <c r="AD47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="AE47" s="29">
-        <f>SUM(O47:AD47)</f>
-        <v>1</v>
-      </c>
+      <c r="AE47" s="31"/>
+      <c r="AF47" s="31"/>
+      <c r="AG47" s="31"/>
+      <c r="AH47" s="31"/>
+      <c r="AI47" s="31"/>
+      <c r="AJ47" s="16">
+        <f>SUM(O47:AI47)</f>
+        <v>1</v>
+      </c>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="47" hidden="1" collapsedDB="0" collapsedOL="0"/>
+        </ext>
+      </extLst>
     </row>
-    <row r="48" spans="1:31" s="32" customFormat="1">
+    <row r="48" spans="1:36" s="32" customFormat="1" hidden="1">
       <c r="A48" s="27"/>
       <c r="D48" s="4" t="n">
         <v>46</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N48" s="30"/>
       <c r="O48" s="30"/>
@@ -4399,20 +4703,30 @@
       <c r="AD48" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="AE48" s="29">
-        <f>SUM(O48:AD48)</f>
-        <v>1</v>
-      </c>
+      <c r="AE48" s="31"/>
+      <c r="AF48" s="31"/>
+      <c r="AG48" s="31"/>
+      <c r="AH48" s="31"/>
+      <c r="AI48" s="31"/>
+      <c r="AJ48" s="16">
+        <f>SUM(O48:AI48)</f>
+        <v>1</v>
+      </c>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:rowDef xmlns:pm="smNativeData" id="1779278746" r="48" hidden="1" collapsedDB="0" collapsedOL="0"/>
+        </ext>
+      </extLst>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="AE1:AE2"/>
+    <mergeCell ref="AJ1:AJ2"/>
     <mergeCell ref="F2:J2"/>
   </mergeCells>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1779109555" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1779278746" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -4421,16 +4735,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1779109555" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1779109555" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1779109555" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1779109555" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1779278746" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1779278746" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1779278746" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1779278746" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1779109555" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1779278746" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
